--- a/data/trending_integrated_20261029_11.xlsx
+++ b/data/trending_integrated_20261029_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4955</v>
+        <v>4980</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.92%</t>
+          <t>'+26.56%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>5986361078</v>
+        <v>6184129537</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9520</v>
+        <v>9340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.15%</t>
+          <t>'+16.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>115667912345</v>
+        <v>117369260175</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37850</v>
+        <v>37400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.76%</t>
+          <t>'+7.47%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>96039282275</v>
+        <v>97463993800</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7980</v>
+        <v>7940</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.11%</t>
+          <t>'+6.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>146</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>94425616880</v>
+        <v>95023483140</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 및 기타 법인 매수세 유입, 반도체 섹터 내 대장주로서의 기대감 고조.</t>
+          <t>외국인 및 기타법인 매수세 유입. 광주 반도체 테마 관련 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인 매수', '대장주', '반도체']</t>
+          <t>['외국인매수', '광주반도체', '테마']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14900</v>
+        <v>14610</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.54%</t>
+          <t>'+1.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>46270434405</v>
+        <v>47569657375</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 내 일부 종목 급등에도 불구하고 주가 하락 및 유증 가능성 언급.</t>
+          <t>의료 AI 섹터 내 단기 변동성 및 유증 가능성 언급. 공매도 관련 불만.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료 AI', '유증', '공매도']</t>
+          <t>['의료AI', '유증', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,184 +1023,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29250</v>
+        <v>1499000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+0.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>477</v>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>1114</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28700</v>
+        <v>1487000</v>
       </c>
       <c r="K7" t="n">
-        <v>29150</v>
+        <v>1511000</v>
       </c>
       <c r="L7" t="n">
-        <v>31400</v>
+        <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>28350</v>
+        <v>1479000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>89969846450</v>
+        <v>4125652295500</v>
       </c>
       <c r="P7" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1850</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>44000</v>
+        <v>337000</v>
       </c>
       <c r="S7" t="n">
-        <v>11000</v>
+        <v>-93000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>삼성전자 대비 상대적 우위 언급. 최태원 회장 긍정 평가 및 분할 매수 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['삼성전자', '분할매수', '투자']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1513000</v>
+        <v>28900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>479</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>1138</v>
+        <v>62</v>
       </c>
       <c r="H8" t="n">
-        <v>48.66</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1487000</v>
+        <v>28700</v>
       </c>
       <c r="K8" t="n">
-        <v>1511000</v>
+        <v>29150</v>
       </c>
       <c r="L8" t="n">
-        <v>1587000</v>
+        <v>31400</v>
       </c>
       <c r="M8" t="n">
-        <v>1479000</v>
+        <v>28350</v>
       </c>
       <c r="N8" t="n">
-        <v>48.61</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>3927943395000</v>
+        <v>91874085625</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>59600</v>
       </c>
       <c r="Q8" t="n">
-        <v>501000</v>
+        <v>1850</v>
       </c>
       <c r="R8" t="n">
-        <v>337000</v>
+        <v>44000</v>
       </c>
       <c r="S8" t="n">
-        <v>-93000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자 대비 상대적 우위 및 시장 내 유일한 투자처로서의 가능성 언급.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성전자', '상대적 우위', '투자처']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14980</v>
+        <v>14870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.46</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="H9" t="n">
         <v>3.33</v>
@@ -1254,7 +1254,7 @@
         <v>2.87</v>
       </c>
       <c r="O9" t="n">
-        <v>127711989715</v>
+        <v>130263056025</v>
       </c>
       <c r="P9" t="n">
         <v>31500</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63100</v>
+        <v>62900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.71%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.54</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="H10" t="n">
         <v>41.55</v>
@@ -1346,7 +1346,7 @@
         <v>41.01</v>
       </c>
       <c r="O10" t="n">
-        <v>124844637300</v>
+        <v>127930153050</v>
       </c>
       <c r="P10" t="n">
         <v>67300</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>185300</v>
+        <v>521000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-2.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="G11" t="n">
-        <v>298</v>
+        <v>1143</v>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
+        <v>24.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>190100</v>
+        <v>534000</v>
       </c>
       <c r="K11" t="n">
-        <v>189400</v>
+        <v>546000</v>
       </c>
       <c r="L11" t="n">
-        <v>197000</v>
+        <v>563000</v>
       </c>
       <c r="M11" t="n">
-        <v>181200</v>
+        <v>512000</v>
       </c>
       <c r="N11" t="n">
-        <v>74.90000000000001</v>
+        <v>24.86</v>
       </c>
       <c r="O11" t="n">
-        <v>939079742150</v>
+        <v>369840017000</v>
       </c>
       <c r="P11" t="n">
-        <v>243500</v>
+        <v>723000</v>
       </c>
       <c r="Q11" t="n">
-        <v>71000</v>
+        <v>259000</v>
       </c>
       <c r="R11" t="n">
-        <v>-409000</v>
+        <v>-24000</v>
       </c>
       <c r="S11" t="n">
-        <v>-172000</v>
+        <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주주환원 불확실성 및 IR 부실에 대한 불만, 우선주 매입 소각 기대.</t>
+          <t>삼성SDI, 26년 3분기 영업이익 추정치 상회 달성. 높은 기대감 속 563,000원 고점 재돌파 카운트다운 진입. ESS, 전고체 관련주 급등 속 대장주로서의 입지 강화.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주주환원', 'IR', '우선주']</t>
+          <t>['영업이익', '컨퍼런스콜', '전고체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>520000</v>
+        <v>25850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.62%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>246</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1123</v>
+        <v>191</v>
       </c>
       <c r="H12" t="n">
-        <v>24.78</v>
+        <v>12.23</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>534000</v>
+        <v>26700</v>
       </c>
       <c r="K12" t="n">
-        <v>546000</v>
+        <v>26350</v>
       </c>
       <c r="L12" t="n">
-        <v>563000</v>
+        <v>26350</v>
       </c>
       <c r="M12" t="n">
-        <v>512000</v>
+        <v>25450</v>
       </c>
       <c r="N12" t="n">
-        <v>24.86</v>
+        <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>358842430500</v>
+        <v>27342167650</v>
       </c>
       <c r="P12" t="n">
-        <v>723000</v>
+        <v>59300</v>
       </c>
       <c r="Q12" t="n">
-        <v>259000</v>
+        <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>-24000</v>
+        <v>-80000</v>
       </c>
       <c r="S12" t="n">
-        <v>9000</v>
+        <v>-15000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성SDI, 23년 3분기 호실적 발표에도 주가 상승 제한적. 26년 3분기 영업이익 컨센서스 상회 예상.</t>
+          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '컨센서스', '전망']</t>
+          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25900</v>
+        <v>8870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="H13" t="n">
-        <v>12.23</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26700</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>26350</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>26350</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>25450</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>12.3</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>26446284750</v>
+        <v>28939940450</v>
       </c>
       <c r="P13" t="n">
-        <v>59300</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>22000</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-80000</v>
+        <v>-47000</v>
       </c>
       <c r="S13" t="n">
-        <v>-15000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8900</v>
+        <v>183000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>149</v>
+        <v>311</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>181200</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>28767531695</v>
+        <v>980673237350</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-47000</v>
+        <v>-409000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-172000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>주주환원 불확실성 및 이재용 리스크에 대한 부정적 의견. 우선주 관련 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['주주환원', '우선주', '컨퍼런스']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15880</v>
+        <v>15840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F15" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H15" t="n">
         <v>28.07</v>
@@ -1806,7 +1806,7 @@
         <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>31211402620</v>
+        <v>32681734255</v>
       </c>
       <c r="P15" t="n">
         <v>35350</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 발표 및 금리 동결, 유가 상승 속에서도 주가 부진에 대한 답답함 토로.</t>
+          <t>주가 하락 및 실적 발표에 대한 실망감. 증권사 및 한국 증시 전반에 대한 불신.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 부진', '조선주']</t>
+          <t>['주가하락', '실적발표', '증권사']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230250</v>
+        <v>227500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-5.99%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G16" t="n">
-        <v>2390</v>
+        <v>2210</v>
       </c>
       <c r="H16" t="n">
         <v>46.19</v>
@@ -1898,7 +1898,7 @@
         <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3358212599250</v>
+        <v>3478406762250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주주환원 불만 및 경영진 교체 요구, 이재용 경영 행태 비판.</t>
+          <t>주주환원 정책 및 경영진에 대한 강한 불만 표출. 이재용 관련 비판.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '경영진 교체', '이재용']</t>
+          <t>['주주환원', '경영진', '상속세']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3990</v>
+        <v>3935</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-6.20%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="H17" t="n">
         <v>2.2</v>
@@ -1990,7 +1990,7 @@
         <v>1.2</v>
       </c>
       <c r="O17" t="n">
-        <v>152899319798</v>
+        <v>154345732521</v>
       </c>
       <c r="P17" t="n">
         <v>8100</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 섹터 내 다른 종목 급등 속에서 주가 부진 및 단기 차익 실현 가능성 언급.</t>
+          <t>광통신 섹터 강세 및 루멘텀 급등에 따른 기대감. 5G 상용화 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '단타', '루멘텀']</t>
+          <t>['광통신', '5G', '루멘텀']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17100</v>
+        <v>1854</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.98%</t>
+          <t>'-11.71%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.46</v>
+        <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="H18" t="n">
-        <v>0.65</v>
+        <v>5.35</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,222 +2067,222 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19210</v>
+        <v>2100</v>
       </c>
       <c r="K18" t="n">
-        <v>19010</v>
+        <v>2120</v>
       </c>
       <c r="L18" t="n">
-        <v>19840</v>
+        <v>2130</v>
       </c>
       <c r="M18" t="n">
-        <v>17060</v>
+        <v>1846</v>
       </c>
       <c r="N18" t="n">
-        <v>1.11</v>
+        <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>79649772780</v>
+        <v>11307339448</v>
       </c>
       <c r="P18" t="n">
-        <v>28800</v>
+        <v>4980</v>
       </c>
       <c r="Q18" t="n">
-        <v>11550</v>
+        <v>810</v>
       </c>
       <c r="R18" t="n">
-        <v>47000</v>
+        <v>43000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 우려 및 반도체 섹터 하락 가능성 속 주가 급락.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체 하락', '주가 급락']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1868</v>
+        <v>54000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.05%</t>
+          <t>'-12.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>703</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>485</v>
       </c>
       <c r="G19" t="n">
-        <v>130</v>
+        <v>2072</v>
       </c>
       <c r="H19" t="n">
-        <v>5.35</v>
+        <v>22.34</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2100</v>
+        <v>61400</v>
       </c>
       <c r="K19" t="n">
-        <v>2120</v>
+        <v>60600</v>
       </c>
       <c r="L19" t="n">
-        <v>2130</v>
+        <v>60800</v>
       </c>
       <c r="M19" t="n">
-        <v>1846</v>
+        <v>53400</v>
       </c>
       <c r="N19" t="n">
-        <v>5.07</v>
+        <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>11156453032</v>
+        <v>234038907550</v>
       </c>
       <c r="P19" t="n">
-        <v>4980</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>810</v>
+        <v>53400</v>
       </c>
       <c r="R19" t="n">
-        <v>43000</v>
+        <v>-1122000</v>
       </c>
       <c r="S19" t="n">
-        <v>10000</v>
+        <v>-389000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
+          <t>체코 원전 시공사 협상 결렬 관련 논란. 두산에너빌리티의 영향 여부 불확실.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트']</t>
+          <t>['체코원전', '시공사', '협상결렬']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>54300</v>
+        <v>16520</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.56%</t>
+          <t>'-14.00%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>670</v>
+        <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>461</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
-        <v>1965</v>
+        <v>103</v>
       </c>
       <c r="H20" t="n">
-        <v>22.34</v>
+        <v>0.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>61400</v>
+        <v>19210</v>
       </c>
       <c r="K20" t="n">
-        <v>60600</v>
+        <v>19010</v>
       </c>
       <c r="L20" t="n">
-        <v>60800</v>
+        <v>19840</v>
       </c>
       <c r="M20" t="n">
-        <v>53400</v>
+        <v>16470</v>
       </c>
       <c r="N20" t="n">
-        <v>22.32</v>
+        <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>226040303750</v>
+        <v>83085498195</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q20" t="n">
-        <v>53400</v>
+        <v>11550</v>
       </c>
       <c r="R20" t="n">
-        <v>-1122000</v>
+        <v>47000</v>
       </c>
       <c r="S20" t="n">
-        <v>-389000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>체코 원전 사업 시공사 변경 관련 논란. 두산에너빌리티는 기자재 공급으로 영향 제한적이라는 분석.</t>
+          <t>보호예수 물량 출회 우려 및 주가 하락 예상. 마이크론 급락 영향.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공사 변경', '기자재 공급']</t>
+          <t>['보호예수', '주가하락', '마이크론']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2175</v>
+        <v>2140</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-15.37%</t>
+          <t>'-16.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2170</v>
+        <v>2140</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>12974727788</v>
+        <v>13544469503</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11270</v>
+        <v>11150</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-21.02%</t>
+          <t>'-21.86%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="F22" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="G22" t="n">
-        <v>1314</v>
+        <v>1414</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>233130693655</v>
+        <v>239521690195</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 악재와 목표가 하향 소식에 따른 주가 하락 우려.</t>
+          <t>체코 원전 사업 관련 변동성으로 인한 주가 하락. 공매도 관련 언급 및 증권사 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['체코 원전', '목표가 하향', '공매도']</t>
+          <t>['체코원전', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_11.xlsx
+++ b/data/trending_integrated_20261029_11.xlsx
@@ -567,18 +567,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4980</v>
+        <v>5010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+26.56%</t>
+          <t>'+27.32%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6184129537</v>
+        <v>6233740209</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9340</v>
+        <v>9370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.90%</t>
+          <t>'+17.27%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
         <v>66</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>117369260175</v>
+        <v>118253734200</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37400</v>
+        <v>37650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.47%</t>
+          <t>'+8.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>97463993800</v>
+        <v>98289818525</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7940</v>
+        <v>7950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.58%</t>
+          <t>'+6.71%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F5" t="n">
         <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>95023483140</v>
+        <v>95335172110</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14610</v>
+        <v>14640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.53%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="H6" t="n">
         <v>8.050000000000001</v>
@@ -978,7 +978,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>47569657375</v>
+        <v>48425324355</v>
       </c>
       <c r="P6" t="n">
         <v>49800</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 내 단기 변동성 및 유증 가능성 언급. 공매도 관련 불만.</t>
+          <t>의료 AI 섹터 급등 및 긍정적 차트 언급. 공매도 세력과의 대립 및 단기 차익 실현 매물 출회 가능성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료AI', '유증', '공매도']</t>
+          <t>['의료 AI', '공매도', '단기 차익']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,254 +1023,254 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1499000</v>
+        <v>29000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.81%</t>
+          <t>'+1.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>477</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>1114</v>
+        <v>62</v>
       </c>
       <c r="H7" t="n">
-        <v>48.66</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1487000</v>
+        <v>28700</v>
       </c>
       <c r="K7" t="n">
-        <v>1511000</v>
+        <v>29150</v>
       </c>
       <c r="L7" t="n">
-        <v>1587000</v>
+        <v>31400</v>
       </c>
       <c r="M7" t="n">
-        <v>1479000</v>
+        <v>28350</v>
       </c>
       <c r="N7" t="n">
-        <v>48.61</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>4125652295500</v>
+        <v>92776808025</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>59600</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>1850</v>
       </c>
       <c r="R7" t="n">
-        <v>337000</v>
+        <v>44000</v>
       </c>
       <c r="S7" t="n">
-        <v>-93000</v>
+        <v>11000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자 대비 상대적 우위 언급. 최태원 회장 긍정 평가 및 분할 매수 권유.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['삼성전자', '분할매수', '투자']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28900</v>
+        <v>1501000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>473</v>
       </c>
       <c r="G8" t="n">
-        <v>62</v>
+        <v>1122</v>
       </c>
       <c r="H8" t="n">
-        <v>1.77</v>
+        <v>48.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28700</v>
+        <v>1487000</v>
       </c>
       <c r="K8" t="n">
-        <v>29150</v>
+        <v>1511000</v>
       </c>
       <c r="L8" t="n">
-        <v>31400</v>
+        <v>1587000</v>
       </c>
       <c r="M8" t="n">
-        <v>28350</v>
+        <v>1479000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>91874085625</v>
+        <v>4220946570500</v>
       </c>
       <c r="P8" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>1850</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>44000</v>
+        <v>337000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>-93000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>삼성전자 대비 상대적 우위 부각 및 시장 내 투자 대안으로 언급. 주가 변동성에 대한 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['삼성전자 비교', '시장 내 대안', '주가 변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14870</v>
+        <v>533000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="G9" t="n">
-        <v>664</v>
+        <v>1188</v>
       </c>
       <c r="H9" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K9" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L9" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M9" t="n">
-        <v>14600</v>
+        <v>512000</v>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>130263056025</v>
+        <v>382669537000</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R9" t="n">
-        <v>-312000</v>
+        <v>-24000</v>
       </c>
       <c r="S9" t="n">
-        <v>42000</v>
+        <v>9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타 관련 뉴스 및 루멘텀 급등에 따른 광통신 섹터 관심 증대. 연말 목표 주가 3만 원 전망.</t>
+          <t>컨퍼런스콜을 통한 호실적 발표 및 미래 전망 긍정. ESS, 전고체 관련주 강세 속 SDI의 대장 역할 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광통신', '메타', '실적 전망']</t>
+          <t>['호실적', '컨퍼런스콜', 'ESS', '전고체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,86 +1292,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62900</v>
+        <v>14830</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>445</v>
+        <v>672</v>
       </c>
       <c r="H10" t="n">
-        <v>41.55</v>
+        <v>3.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>64200</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>64200</v>
+        <v>15120</v>
       </c>
       <c r="L10" t="n">
-        <v>65500</v>
+        <v>15950</v>
       </c>
       <c r="M10" t="n">
-        <v>62500</v>
+        <v>14600</v>
       </c>
       <c r="N10" t="n">
-        <v>41.01</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>127930153050</v>
+        <v>131914430965</v>
       </c>
       <c r="P10" t="n">
-        <v>67300</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>23150</v>
+        <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>408000</v>
+        <v>-312000</v>
       </c>
       <c r="S10" t="n">
-        <v>-60000</v>
+        <v>42000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 가능성, 자사주 매입 기반 주가 방어 기대.</t>
+          <t>메타 관련 뉴스 및 루멘텀 급등에 따른 광통신 섹터 관심 증대. 연말 목표 주가 3만 원 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['수주 공시', '신고가', '자사주 매입']</t>
+          <t>['광통신', '메타', '실적 전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>521000</v>
+        <v>62700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.43%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>251</v>
+        <v>92</v>
       </c>
       <c r="F11" t="n">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>1143</v>
+        <v>461</v>
       </c>
       <c r="H11" t="n">
-        <v>24.78</v>
+        <v>41.55</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>534000</v>
+        <v>64200</v>
       </c>
       <c r="K11" t="n">
-        <v>546000</v>
+        <v>64200</v>
       </c>
       <c r="L11" t="n">
-        <v>563000</v>
+        <v>65500</v>
       </c>
       <c r="M11" t="n">
-        <v>512000</v>
+        <v>62500</v>
       </c>
       <c r="N11" t="n">
-        <v>24.86</v>
+        <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>369840017000</v>
+        <v>130819008950</v>
       </c>
       <c r="P11" t="n">
-        <v>723000</v>
+        <v>67300</v>
       </c>
       <c r="Q11" t="n">
-        <v>259000</v>
+        <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>-24000</v>
+        <v>408000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>-60000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성SDI, 26년 3분기 영업이익 추정치 상회 달성. 높은 기대감 속 563,000원 고점 재돌파 카운트다운 진입. ESS, 전고체 관련주 급등 속 대장주로서의 입지 강화.</t>
+          <t>수주 공시 및 신고가 도전 가능성, 자사주 매입 기반 주가 방어 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '컨퍼런스콜', '전고체']</t>
+          <t>['수주 공시', '신고가', '자사주 매입']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25850</v>
+        <v>25950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
         <v>12.23</v>
@@ -1530,7 +1530,7 @@
         <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>27342167650</v>
+        <v>28490427500</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8870</v>
+        <v>15860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.94%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.37</v>
+        <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>28.07</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9180</v>
+        <v>16510</v>
       </c>
       <c r="K13" t="n">
-        <v>9200</v>
+        <v>16380</v>
       </c>
       <c r="L13" t="n">
-        <v>10900</v>
+        <v>16440</v>
       </c>
       <c r="M13" t="n">
-        <v>8730</v>
+        <v>15770</v>
       </c>
       <c r="N13" t="n">
-        <v>0.74</v>
+        <v>28.03</v>
       </c>
       <c r="O13" t="n">
-        <v>28939940450</v>
+        <v>33748601790</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>15770</v>
       </c>
       <c r="R13" t="n">
-        <v>-47000</v>
+        <v>-48000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>지속적인 신저점 갱신 및 주가 부진에 대한 불만. 실적 및 향후 전망에 대한 부정적 시각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['신저점 갱신', '주가 부진', '향후 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183000</v>
+        <v>8815</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.73%</t>
+          <t>'-3.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>-0.37</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="G14" t="n">
-        <v>311</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>0.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>190100</v>
+        <v>9180</v>
       </c>
       <c r="K14" t="n">
-        <v>189400</v>
+        <v>9200</v>
       </c>
       <c r="L14" t="n">
-        <v>197000</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>181200</v>
+        <v>8730</v>
       </c>
       <c r="N14" t="n">
-        <v>74.90000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>980673237350</v>
+        <v>29005002485</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>71000</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-409000</v>
+        <v>-47000</v>
       </c>
       <c r="S14" t="n">
-        <v>-172000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주주환원 불확실성 및 이재용 리스크에 대한 부정적 의견. 우선주 관련 언급.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주주환원', '우선주', '컨퍼런스']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15840</v>
+        <v>182400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G15" t="n">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="H15" t="n">
-        <v>28.07</v>
+        <v>75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16510</v>
+        <v>190100</v>
       </c>
       <c r="K15" t="n">
-        <v>16380</v>
+        <v>189400</v>
       </c>
       <c r="L15" t="n">
-        <v>16440</v>
+        <v>197000</v>
       </c>
       <c r="M15" t="n">
-        <v>15770</v>
+        <v>181200</v>
       </c>
       <c r="N15" t="n">
-        <v>28.03</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>32681734255</v>
+        <v>1012898574800</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>15770</v>
+        <v>71000</v>
       </c>
       <c r="R15" t="n">
-        <v>-48000</v>
+        <v>-409000</v>
       </c>
       <c r="S15" t="n">
-        <v>-70000</v>
+        <v>-172000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 실적 발표에 대한 실망감. 증권사 및 한국 증시 전반에 대한 불신.</t>
+          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 우려. IR 부족 및 실적 발표 후 주가 하락.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가하락', '실적발표', '증권사']</t>
+          <t>['오너 리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>227500</v>
+        <v>3980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.99%</t>
+          <t>'-5.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>618</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
-        <v>2210</v>
+        <v>235</v>
       </c>
       <c r="H16" t="n">
-        <v>46.19</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>242000</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>241000</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>249000</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>227000</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>46.15</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3478406762250</v>
+        <v>155235706867</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-197000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주주환원 정책 및 경영진에 대한 강한 불만 표출. 이재용 관련 비판.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작 뉴스에 따른 광통신 섹터 강세. 루멘텀의 급등 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '경영진', '상속세']</t>
+          <t>['5G 상용화', '광통신 섹터', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3935</v>
+        <v>226750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.20%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>614</v>
       </c>
       <c r="G17" t="n">
-        <v>230</v>
+        <v>2063</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>46.19</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4195</v>
+        <v>242000</v>
       </c>
       <c r="K17" t="n">
-        <v>4280</v>
+        <v>241000</v>
       </c>
       <c r="L17" t="n">
-        <v>4480</v>
+        <v>249000</v>
       </c>
       <c r="M17" t="n">
-        <v>3915</v>
+        <v>226000</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2</v>
+        <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>154345732521</v>
+        <v>3579944174500</v>
       </c>
       <c r="P17" t="n">
-        <v>8100</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>592</v>
+        <v>94500</v>
       </c>
       <c r="R17" t="n">
-        <v>-190000</v>
+        <v>-197000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 루멘텀 급등에 따른 기대감. 5G 상용화 관련 뉴스 언급.</t>
+          <t>주주환원 정책 미흡 및 경영진 비판. 상속세 이슈와 연계된 소액주주 불만 고조.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '5G', '루멘텀']</t>
+          <t>['주주환원', '상속세', '경영진']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.71%</t>
+          <t>'-11.67%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>11307339448</v>
+        <v>11563581908</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54000</v>
+        <v>53800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.05%</t>
+          <t>'-12.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="F19" t="n">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="G19" t="n">
-        <v>2072</v>
+        <v>2118</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>234038907550</v>
+        <v>242054776100</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16520</v>
+        <v>16570</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-14.00%</t>
+          <t>'-13.74%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2260,13 +2260,13 @@
         <v>19840</v>
       </c>
       <c r="M20" t="n">
-        <v>16470</v>
+        <v>16400</v>
       </c>
       <c r="N20" t="n">
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>83085498195</v>
+        <v>84224493935</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 우려 및 주가 하락 예상. 마이크론 급락 영향.</t>
+          <t>보호예수 물량 출회 및 주가 폭락에 대한 경고. 반도체 섹터 하락 영향 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '주가하락', '마이크론']</t>
+          <t>['보호예수 물량', '주가 폭락', '반도체 하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,10 +2326,10 @@
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>79</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>13544469503</v>
+        <v>13799405998</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11150</v>
+        <v>11270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-21.86%</t>
+          <t>'-21.02%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="F22" t="n">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G22" t="n">
-        <v>1414</v>
+        <v>1486</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>239521690195</v>
+        <v>244769779415</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 변동성으로 인한 주가 하락. 공매도 관련 언급 및 증권사 비판.</t>
+          <t>체코 원전 사업 탈락에 따른 목표가 하향 조정 및 과매도 구간 진입 전망. 공매도 세력의 작전 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['체코원전', '공매도', '목표가']</t>
+          <t>['체코 원전', '목표가 하향', '과매도']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_11.xlsx
+++ b/data/trending_integrated_20261029_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5010</v>
+        <v>5100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.32%</t>
+          <t>'+29.61%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6233740209</v>
+        <v>6383331169</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9370</v>
+        <v>9490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.27%</t>
+          <t>'+18.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>118253734200</v>
+        <v>119474814965</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37650</v>
+        <v>37750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>98289818525</v>
+        <v>100015342100</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7950</v>
+        <v>7860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.71%</t>
+          <t>'+5.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>95335172110</v>
+        <v>96156492000</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 및 기타법인 매수세 유입. 광주 반도체 테마 관련 기대감.</t>
+          <t>외국인 및 기타 법인의 대규모 매수세 유입 확인. 광주 반도체 테마 편입 및 차트상 안정적인 흐름 예상에 따른 매수 기회 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인매수', '광주반도체', '테마']</t>
+          <t>['외국인 매수', '광주 반도체', '차트 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14640</v>
+        <v>29000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>281</v>
+        <v>71</v>
       </c>
       <c r="H6" t="n">
-        <v>8.050000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,235 +963,235 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14390</v>
+        <v>28700</v>
       </c>
       <c r="K6" t="n">
-        <v>15450</v>
+        <v>29150</v>
       </c>
       <c r="L6" t="n">
-        <v>16290</v>
+        <v>31400</v>
       </c>
       <c r="M6" t="n">
-        <v>14040</v>
+        <v>28350</v>
       </c>
       <c r="N6" t="n">
-        <v>8.109999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>48425324355</v>
+        <v>94362161300</v>
       </c>
       <c r="P6" t="n">
-        <v>49800</v>
+        <v>59600</v>
       </c>
       <c r="Q6" t="n">
-        <v>8180</v>
+        <v>1850</v>
       </c>
       <c r="R6" t="n">
-        <v>-238000</v>
+        <v>44000</v>
       </c>
       <c r="S6" t="n">
         <v>11000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 급등 및 긍정적 차트 언급. 공매도 세력과의 대립 및 단기 차익 실현 매물 출회 가능성.</t>
+          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '단기 차익']</t>
+          <t>['루멘텀', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29000</v>
+        <v>1497000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.05%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>472</v>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>1090</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28700</v>
+        <v>1487000</v>
       </c>
       <c r="K7" t="n">
-        <v>29150</v>
+        <v>1511000</v>
       </c>
       <c r="L7" t="n">
-        <v>31400</v>
+        <v>1587000</v>
       </c>
       <c r="M7" t="n">
-        <v>28350</v>
+        <v>1479000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>92776808025</v>
+        <v>4322129275000</v>
       </c>
       <c r="P7" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>1850</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>44000</v>
+        <v>337000</v>
       </c>
       <c r="S7" t="n">
-        <v>11000</v>
+        <v>-93000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>루멘텀홀딩스 인수 관련 호재 및 기관 매수세 언급. 광통신주 동반 하락으로 인한 관망세.</t>
+          <t>삼성전자와의 상대적 비교 우위 부각 및 한국 증시 내 유일한 투자처로서의 긍정적 평가. 꾸준한 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['루멘텀', '기관']</t>
+          <t>['삼성전자', '상대적 우위', '투자처']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1501000</v>
+        <v>14470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>1122</v>
+        <v>288</v>
       </c>
       <c r="H8" t="n">
-        <v>48.66</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1487000</v>
+        <v>14390</v>
       </c>
       <c r="K8" t="n">
-        <v>1511000</v>
+        <v>15450</v>
       </c>
       <c r="L8" t="n">
-        <v>1587000</v>
+        <v>16290</v>
       </c>
       <c r="M8" t="n">
-        <v>1479000</v>
+        <v>14040</v>
       </c>
       <c r="N8" t="n">
-        <v>48.61</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>4220946570500</v>
+        <v>49318289910</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>501000</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>337000</v>
+        <v>-238000</v>
       </c>
       <c r="S8" t="n">
-        <v>-93000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자 대비 상대적 우위 부각 및 시장 내 투자 대안으로 언급. 주가 변동성에 대한 언급.</t>
+          <t>미국 의료 AI 섹터 급등에 따른 시초 상승 기대감. 다만, 단기 급등 후 본장 무너짐 우려 및 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성전자 비교', '시장 내 대안', '주가 변동성']</t>
+          <t>['의료 AI', '공매도', '단타']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>533000</v>
+        <v>534000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="F9" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G9" t="n">
-        <v>1188</v>
+        <v>1257</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>382669537000</v>
+        <v>403004691000</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>컨퍼런스콜을 통한 호실적 발표 및 미래 전망 긍정. ESS, 전고체 관련주 강세 속 SDI의 대장 역할 부각.</t>
+          <t>26년 3분기 영업이익 컨센서스 상회 및 전고체 배터리 내년 하반기 상용화 관련 긍정적인 컨퍼런스콜 내용.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['호실적', '컨퍼런스콜', 'ESS', '전고체']</t>
+          <t>['컨퍼런스콜', '전고체 배터리', '영업이익']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14830</v>
+        <v>14870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.00%</t>
+          <t>'-0.73%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>131914430965</v>
+        <v>133915459220</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62700</v>
+        <v>26300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.34%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.54</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>461</v>
+        <v>210</v>
       </c>
       <c r="H11" t="n">
-        <v>41.55</v>
+        <v>12.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>64200</v>
+        <v>26700</v>
       </c>
       <c r="K11" t="n">
-        <v>64200</v>
+        <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>65500</v>
+        <v>26400</v>
       </c>
       <c r="M11" t="n">
-        <v>62500</v>
+        <v>25450</v>
       </c>
       <c r="N11" t="n">
-        <v>41.01</v>
+        <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>130819008950</v>
+        <v>31439122975</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>59300</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>408000</v>
+        <v>-80000</v>
       </c>
       <c r="S11" t="n">
-        <v>-60000</v>
+        <v>-15000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 가능성, 자사주 매입 기반 주가 방어 기대.</t>
+          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주 공시', '신고가', '자사주 매입']</t>
+          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25950</v>
+        <v>62800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>482</v>
       </c>
       <c r="H12" t="n">
-        <v>12.23</v>
+        <v>41.55</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26700</v>
+        <v>64200</v>
       </c>
       <c r="K12" t="n">
-        <v>26350</v>
+        <v>64200</v>
       </c>
       <c r="L12" t="n">
-        <v>26350</v>
+        <v>65500</v>
       </c>
       <c r="M12" t="n">
-        <v>25450</v>
+        <v>62500</v>
       </c>
       <c r="N12" t="n">
-        <v>12.3</v>
+        <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>28490427500</v>
+        <v>133544601850</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-80000</v>
+        <v>408000</v>
       </c>
       <c r="S12" t="n">
-        <v>-15000</v>
+        <v>-60000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
+          <t>자사주 매입 및 소각 관련 긍정적 신호 포착. 수소 에너지 사업 기대감과 함께 신고가 경신 가능성에 대한 전망 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
+          <t>['자사주 소각', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15860</v>
+        <v>8880</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>294</v>
+        <v>153</v>
       </c>
       <c r="H13" t="n">
-        <v>28.07</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16510</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>16380</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>16440</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>15770</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>28.03</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>33748601790</v>
+        <v>29118952890</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>15770</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-48000</v>
+        <v>-47000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>-1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>지속적인 신저점 갱신 및 주가 부진에 대한 불만. 실적 및 향후 전망에 대한 부정적 시각.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['신저점 갱신', '주가 부진', '향후 전망']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8815</v>
+        <v>15860</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.98%</t>
+          <t>'-3.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>28.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>16510</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>16380</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>16440</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>15770</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>29005002485</v>
+        <v>34976324200</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>15770</v>
       </c>
       <c r="R14" t="n">
-        <v>-47000</v>
+        <v>-48000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>-70000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['실적 부진', '신저점', '조선업']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>182400</v>
+        <v>182500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="H15" t="n">
         <v>75</v>
@@ -1806,7 +1806,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1012898574800</v>
+        <v>1043574711850</v>
       </c>
       <c r="P15" t="n">
         <v>243500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 우려. IR 부족 및 실적 발표 후 주가 하락.</t>
+          <t>삼성전자 우선주 관련 주주환원 불확실성 및 IR 부실에 대한 비판. 오너 리스크와 증여세 이슈가 부정적 요인으로 작용.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', 'IR']</t>
+          <t>['우선주', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3980</v>
+        <v>3992</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.13%</t>
+          <t>'-4.84%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
         <v>2.2</v>
@@ -1898,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>155235706867</v>
+        <v>156618178161</v>
       </c>
       <c r="P16" t="n">
         <v>8100</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작 뉴스에 따른 광통신 섹터 강세. 루멘텀의 급등 언급.</t>
+          <t>광통신 섹터 내 타 종목(루멘텀)의 급등과 비교되며 상대적 주가 부진에 대한 아쉬움 표출. 단기 차익 실현 매물 출회 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G 상용화', '광통신 섹터', '글로벌 공급']</t>
+          <t>['광통신', '루멘텀', '단타']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>226750</v>
+        <v>227500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.30%</t>
+          <t>'-5.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="G17" t="n">
-        <v>2063</v>
+        <v>2023</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3579944174500</v>
+        <v>3670429577750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주환원 정책 미흡 및 경영진 비판. 상속세 이슈와 연계된 소액주주 불만 고조.</t>
+          <t>컨퍼런스콜에서의 소극적인 주주환원 정책 및 경영진에 대한 불만 고조. 하이닉스와의 비교를 통한 상대적 비판 및 불매 운동 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주환원', '상속세', '경영진']</t>
+          <t>['컨퍼런스콜', '주주환원', '이재용']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1855</v>
+        <v>1861</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.67%</t>
+          <t>'-11.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>11563581908</v>
+        <v>11669756950</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53800</v>
+        <v>53850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.38%</t>
+          <t>'-12.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="F19" t="n">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="G19" t="n">
-        <v>2118</v>
+        <v>2184</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>242054776100</v>
+        <v>249061489050</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 시공사 협상 결렬 관련 논란. 두산에너빌리티의 영향 여부 불확실.</t>
+          <t>체코 원전 시공사 협상 결렬에도 불구하고, 기자재 공급사인 두산에 대한 영향은 제한적이라는 분석. 언론 보도의 부정확성에 대한 지적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코원전', '시공사', '협상결렬']</t>
+          <t>['체코 원전', '기자재', '시공사']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16570</v>
+        <v>16720</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.74%</t>
+          <t>'-12.96%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>84224493935</v>
+        <v>85711341060</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 주가 폭락에 대한 경고. 반도체 섹터 하락 영향 가능성 언급.</t>
+          <t>보호예수 물량 해제 및 반도체 섹터 전반의 하락세에 따른 추가 하락 가능성 경고. 무분별한 희망 회로에 대한 비판.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수 물량', '주가 폭락', '반도체 하락']</t>
+          <t>['보호예수', '반도체 하락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.73%</t>
+          <t>'-16.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>13799405998</v>
+        <v>14068927790</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11270</v>
+        <v>11230</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-21.02%</t>
+          <t>'-21.30%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="F22" t="n">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="G22" t="n">
-        <v>1486</v>
+        <v>1592</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>244769779415</v>
+        <v>250410406615</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>체코 원전 사업 탈락에 따른 목표가 하향 조정 및 과매도 구간 진입 전망. 공매도 세력의 작전 의혹 제기.</t>
+          <t>체코 원전 사업 관련 악재로 인한 과매도 구간 진입 및 목표가 하향 조정. 하지만 공매도 세력의 과도한 하락 유도에 대한 반발 심리 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['체코 원전', '목표가 하향', '과매도']</t>
+          <t>['체코 원전', '공매도', '과매도']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_11.xlsx
+++ b/data/trending_integrated_20261029_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.61%</t>
+          <t>'+28.34%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
         <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6383331169</v>
+        <v>6476518679</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9490</v>
+        <v>9520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.77%</t>
+          <t>'+19.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>119474814965</v>
+        <v>120567627880</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37750</v>
+        <v>38000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+9.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>100015342100</v>
+        <v>100845857450</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7860</v>
+        <v>8020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.50%</t>
+          <t>'+7.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>96156492000</v>
+        <v>97615823895</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29000</v>
+        <v>29250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.05%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -978,7 +978,7 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>94362161300</v>
+        <v>95059945725</v>
       </c>
       <c r="P6" t="n">
         <v>59600</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1497000</v>
+        <v>1501000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G7" t="n">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4322129275000</v>
+        <v>4410900345500</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자와의 상대적 비교 우위 부각 및 한국 증시 내 유일한 투자처로서의 긍정적 평가. 꾸준한 매수 의견 제시.</t>
+          <t>삼성전자 대비 상대적 우위 강조. 국장 내 투자처로서의 SK하이닉스 부각. 최태원 회장의 경영 능력 긍정 평가.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['삼성전자', '상대적 우위', '투자처']</t>
+          <t>['상대적우위', '국내증시', '최태원']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14470</v>
+        <v>14480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+0.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G8" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H8" t="n">
         <v>8.050000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>49318289910</v>
+        <v>49952403325</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>534000</v>
+        <v>537000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G9" t="n">
-        <v>1257</v>
+        <v>1333</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>403004691000</v>
+        <v>411228091500</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14870</v>
+        <v>14940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>133915459220</v>
+        <v>134838862020</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26300</v>
+        <v>26350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>31439122975</v>
+        <v>31988279125</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62800</v>
+        <v>62900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.18%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>133544601850</v>
+        <v>136214268200</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8880</v>
+        <v>183600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G13" t="n">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K13" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L13" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M13" t="n">
-        <v>8730</v>
+        <v>181200</v>
       </c>
       <c r="N13" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>29118952890</v>
+        <v>1065553999900</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R13" t="n">
-        <v>-47000</v>
+        <v>-409000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>-172000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>오너 리스크와 불확실한 주주환원 정책 지적. 허접한 IR 및 컨퍼런스콜 내용에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['오너리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15860</v>
+        <v>8860</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-3.49%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>-0.37</v>
       </c>
       <c r="E14" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
-        <v>308</v>
+        <v>155</v>
       </c>
       <c r="H14" t="n">
-        <v>28.07</v>
+        <v>0.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,139 +1699,139 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16510</v>
+        <v>9180</v>
       </c>
       <c r="K14" t="n">
-        <v>16380</v>
+        <v>9200</v>
       </c>
       <c r="L14" t="n">
-        <v>16440</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>15770</v>
+        <v>8730</v>
       </c>
       <c r="N14" t="n">
-        <v>28.03</v>
+        <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>34976324200</v>
+        <v>29271125910</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>15770</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-48000</v>
+        <v>-47000</v>
       </c>
       <c r="S14" t="n">
-        <v>-70000</v>
+        <v>-1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 부진', '신저점', '조선업']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>182500</v>
+        <v>4040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>334</v>
+        <v>255</v>
       </c>
       <c r="H15" t="n">
-        <v>75</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>190100</v>
+        <v>4195</v>
       </c>
       <c r="K15" t="n">
-        <v>189400</v>
+        <v>4280</v>
       </c>
       <c r="L15" t="n">
-        <v>197000</v>
+        <v>4480</v>
       </c>
       <c r="M15" t="n">
-        <v>181200</v>
+        <v>3915</v>
       </c>
       <c r="N15" t="n">
-        <v>74.90000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1043574711850</v>
+        <v>158578212941</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>71000</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-409000</v>
+        <v>-190000</v>
       </c>
       <c r="S15" t="n">
-        <v>-172000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 우선주 관련 주주환원 불확실성 및 IR 부실에 대한 비판. 오너 리스크와 증여세 이슈가 부정적 요인으로 작용.</t>
+          <t>광통신 섹터의 주도주 부각 및 루멘텀 폭등 언급. 5G 상용화망 성공 뉴스 및 글로벌 공급 시작 호재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', 'IR']</t>
+          <t>['광통신', '5G', '루멘텀']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3992</v>
+        <v>15850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.84%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>15770</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>156618178161</v>
+        <v>35635730440</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>15770</v>
       </c>
       <c r="R16" t="n">
-        <v>-190000</v>
+        <v>-48000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>광통신 섹터 내 타 종목(루멘텀)의 급등과 비교되며 상대적 주가 부진에 대한 아쉬움 표출. 단기 차익 실현 매물 출회 가능성 언급.</t>
+          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '단타']</t>
+          <t>['실적 부진', '신저점', '조선업']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>227500</v>
+        <v>228000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.99%</t>
+          <t>'-5.79%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="G17" t="n">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3670429577750</v>
+        <v>3718337703250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>컨퍼런스콜에서의 소극적인 주주환원 정책 및 경영진에 대한 불만 고조. 하이닉스와의 비교를 통한 상대적 비판 및 불매 운동 언급.</t>
+          <t>이재용 경영진의 불법 승계, 세무 조사, 주주 소통 부재에 대한 강한 불만 제기. 컨퍼런스콜의 미흡함 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '주주환원', '이재용']</t>
+          <t>['불법승계', '컨퍼런스콜', '주주소통']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.38%</t>
+          <t>'-11.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
         <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>11669756950</v>
+        <v>11756416592</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53850</v>
+        <v>54000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.30%</t>
+          <t>'-12.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>746</v>
+        <v>780</v>
       </c>
       <c r="F19" t="n">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="G19" t="n">
-        <v>2184</v>
+        <v>2233</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>249061489050</v>
+        <v>253995870450</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16720</v>
+        <v>16730</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-12.96%</t>
+          <t>'-12.91%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>85711341060</v>
+        <v>86150231590</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제 및 반도체 섹터 전반의 하락세에 따른 추가 하락 가능성 경고. 무분별한 희망 회로에 대한 비판.</t>
+          <t>보호 예수 물량 출회 및 반도체 섹터 대폭락 경고. 주포의 매도 이유 부재 및 개미 털기 가능성 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체 하락', '주포']</t>
+          <t>['보호예수', '반도체', '개미털기']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.54%</t>
+          <t>'-16.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2352,13 +2352,13 @@
         <v>2575</v>
       </c>
       <c r="M21" t="n">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="N21" t="n">
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>14068927790</v>
+        <v>14394254191</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11230</v>
+        <v>11280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-21.30%</t>
+          <t>'-20.95%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="F22" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G22" t="n">
-        <v>1592</v>
+        <v>1659</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>250410406615</v>
+        <v>253676286805</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 악재로 인한 과매도 구간 진입 및 목표가 하향 조정. 하지만 공매도 세력의 과도한 하락 유도에 대한 반발 심리 존재.</t>
+          <t>단기 악재 및 과매도 상황 언급. 공매도 세력과 증권사 창구 매도세 지적. 원전 계약 관련 정부 실수 및 과도한 공사비 삭감 요구 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['체코 원전', '공매도', '과매도']</t>
+          <t>['공매도', '과매도', '원전계약']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_11.xlsx
+++ b/data/trending_integrated_20261029_11.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5050</v>
+        <v>5110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+28.34%</t>
+          <t>'+29.86%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6476518679</v>
+        <v>6687909099</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9520</v>
+        <v>9430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.15%</t>
+          <t>'+18.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>120567627880</v>
+        <v>121627088490</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38000</v>
+        <v>38200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
         <v>126</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>100845857450</v>
+        <v>101978653800</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8020</v>
+        <v>7770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.65%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>97615823895</v>
+        <v>100155444165</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 및 기타 법인의 대규모 매수세 유입 확인. 광주 반도체 테마 편입 및 차트상 안정적인 흐름 예상에 따른 매수 기회 제시.</t>
+          <t>외국인 및 기타법인 매수세 유입. 광주 반도체 테마 및 수급 개선에 따른 상승 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인 매수', '광주 반도체', '차트 분석']</t>
+          <t>['외국인 매수', '광주 반도체', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29250</v>
+        <v>29500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -978,7 +978,7 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>95059945725</v>
+        <v>96227881075</v>
       </c>
       <c r="P6" t="n">
         <v>59600</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1501000</v>
+        <v>1513000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="G7" t="n">
-        <v>1095</v>
+        <v>1118</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4410900345500</v>
+        <v>4480447331000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자 대비 상대적 우위 강조. 국장 내 투자처로서의 SK하이닉스 부각. 최태원 회장의 경영 능력 긍정 평가.</t>
+          <t>삼성전자 대비 SK하이닉스의 상대적 우위 및 독립적인 주가 흐름 기대. 투자 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['상대적우위', '국내증시', '최태원']</t>
+          <t>['SK하이닉스', '삼성전자', '독립']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14480</v>
+        <v>542000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.63%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>306</v>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="G8" t="n">
-        <v>292</v>
+        <v>1364</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>24.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>534000</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>546000</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>563000</v>
       </c>
       <c r="M8" t="n">
-        <v>14040</v>
+        <v>512000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>49952403325</v>
+        <v>421409381500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>723000</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>259000</v>
       </c>
       <c r="R8" t="n">
-        <v>-238000</v>
+        <v>-24000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 급등에 따른 시초 상승 기대감. 다만, 단기 급등 후 본장 무너짐 우려 및 공매도 세력에 대한 언급.</t>
+          <t>호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 및 미래 성장 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '단타']</t>
+          <t>['호실적', '전고체 배터리', '컨센서스']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>537000</v>
+        <v>14420</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+0.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>303</v>
+        <v>116</v>
       </c>
       <c r="F9" t="n">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>1333</v>
+        <v>301</v>
       </c>
       <c r="H9" t="n">
-        <v>24.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>534000</v>
+        <v>14390</v>
       </c>
       <c r="K9" t="n">
-        <v>546000</v>
+        <v>15450</v>
       </c>
       <c r="L9" t="n">
-        <v>563000</v>
+        <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>512000</v>
+        <v>14040</v>
       </c>
       <c r="N9" t="n">
-        <v>24.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>411228091500</v>
+        <v>50521197090</v>
       </c>
       <c r="P9" t="n">
-        <v>723000</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>259000</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-24000</v>
+        <v>-238000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>26년 3분기 영업이익 컨센서스 상회 및 전고체 배터리 내년 하반기 상용화 관련 긍정적인 컨퍼런스콜 내용.</t>
+          <t>미국 의료 AI 종목 급등에 따른 기대감. 단기 급등 후 조정 및 하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '전고체 배터리', '영업이익']</t>
+          <t>['의료 AI', '미국 시장', '단기 조정']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14940</v>
+        <v>14950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G10" t="n">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>134838862020</v>
+        <v>136247298215</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26350</v>
+        <v>26550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-0.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1429,7 +1429,7 @@
         <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>26400</v>
+        <v>26550</v>
       </c>
       <c r="M11" t="n">
         <v>25450</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>31988279125</v>
+        <v>32884110400</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62900</v>
+        <v>63100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" t="n">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>136214268200</v>
+        <v>138589002750</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>183600</v>
+        <v>184500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.42%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G13" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="H13" t="n">
         <v>75</v>
@@ -1622,7 +1622,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1065553999900</v>
+        <v>1084776252550</v>
       </c>
       <c r="P13" t="n">
         <v>243500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>오너 리스크와 불확실한 주주환원 정책 지적. 허접한 IR 및 컨퍼런스콜 내용에 대한 불만.</t>
+          <t>오너 리스크 및 주주환원 불확실성에 대한 우려. IR 역량 부족 지적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너리스크', '주주환원', 'IR']</t>
+          <t>['오너 리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8860</v>
+        <v>8870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.49%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>29271125910</v>
+        <v>29393239540</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4040</v>
+        <v>15870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>255</v>
+        <v>333</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>15770</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>158578212941</v>
+        <v>36544411810</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>15770</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-48000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광통신 섹터의 주도주 부각 및 루멘텀 폭등 언급. 5G 상용화망 성공 뉴스 및 글로벌 공급 시작 호재.</t>
+          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '5G', '루멘텀']</t>
+          <t>['실적 부진', '신저점', '조선업']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15850</v>
+        <v>4030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
+        <v>269</v>
       </c>
       <c r="H16" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>15770</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>35635730440</v>
+        <v>159727721189</v>
       </c>
       <c r="P16" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>15770</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-48000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>신저점 갱신 및 실적 부진으로 인한 투자자 불만 고조. 중국 조선업체와의 경쟁 열세 및 한국 증권사의 부정적 영향력 언급.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작 뉴스에 따른 광통신 섹터 주목. 루멘텀 폭등.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적 부진', '신저점', '조선업']</t>
+          <t>['5G 상용화', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>228000</v>
+        <v>229500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.79%</t>
+          <t>'-5.17%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="G17" t="n">
-        <v>2027</v>
+        <v>2093</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3718337703250</v>
+        <v>3773559387750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>이재용 경영진의 불법 승계, 세무 조사, 주주 소통 부재에 대한 강한 불만 제기. 컨퍼런스콜의 미흡함 비판.</t>
+          <t>주주환원 정책에 대한 강한 불만 제기. 이재용 경영 스타일 및 IR 역량 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['불법승계', '컨퍼런스콜', '주주소통']</t>
+          <t>['주주환원', '이재용', 'IR']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,184 +2035,184 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1862</v>
+        <v>54450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.33%</t>
+          <t>'-11.32%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>62</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>539</v>
       </c>
       <c r="G18" t="n">
-        <v>143</v>
+        <v>2302</v>
       </c>
       <c r="H18" t="n">
-        <v>5.35</v>
+        <v>22.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2100</v>
+        <v>61400</v>
       </c>
       <c r="K18" t="n">
-        <v>2120</v>
+        <v>60600</v>
       </c>
       <c r="L18" t="n">
-        <v>2130</v>
+        <v>60800</v>
       </c>
       <c r="M18" t="n">
-        <v>1846</v>
+        <v>53400</v>
       </c>
       <c r="N18" t="n">
-        <v>5.07</v>
+        <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>11756416592</v>
+        <v>260168753800</v>
       </c>
       <c r="P18" t="n">
-        <v>4980</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>810</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>43000</v>
+        <v>-1122000</v>
       </c>
       <c r="S18" t="n">
-        <v>10000</v>
+        <v>-389000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
+          <t>체코 원전 시공사 협상 결렬에도 기자재 공급은 유지된다는 분석. 현 정부 및 특정 정치인 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트']</t>
+          <t>['체코 원전', '기자재', '시공사']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>54000</v>
+        <v>1853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.05%</t>
+          <t>'-11.76%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>780</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>531</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>2233</v>
+        <v>139</v>
       </c>
       <c r="H19" t="n">
-        <v>22.34</v>
+        <v>5.35</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>61400</v>
+        <v>2100</v>
       </c>
       <c r="K19" t="n">
-        <v>60600</v>
+        <v>2120</v>
       </c>
       <c r="L19" t="n">
-        <v>60800</v>
+        <v>2130</v>
       </c>
       <c r="M19" t="n">
-        <v>53400</v>
+        <v>1846</v>
       </c>
       <c r="N19" t="n">
-        <v>22.32</v>
+        <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>253995870450</v>
+        <v>11881344926</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>4980</v>
       </c>
       <c r="Q19" t="n">
-        <v>53400</v>
+        <v>810</v>
       </c>
       <c r="R19" t="n">
-        <v>-1122000</v>
+        <v>43000</v>
       </c>
       <c r="S19" t="n">
-        <v>-389000</v>
+        <v>10000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 시공사 협상 결렬에도 불구하고, 기자재 공급사인 두산에 대한 영향은 제한적이라는 분석. 언론 보도의 부정확성에 대한 지적.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코 원전', '기자재', '시공사']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16730</v>
+        <v>16790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-12.91%</t>
+          <t>'-12.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>86150231590</v>
+        <v>86585133925</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호 예수 물량 출회 및 반도체 섹터 대폭락 경고. 주포의 매도 이유 부재 및 개미 털기 가능성 언급.</t>
+          <t>보호 예수 물량 폭탄 및 반도체 대폭락 가능성 경고. 급락세에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '개미털기']</t>
+          <t>['보호 예수', '반도체 대폭락', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.73%</t>
+          <t>'-16.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.47</v>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" t="n">
         <v>1.22</v>
@@ -2358,7 +2358,7 @@
         <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>14394254191</v>
+        <v>14586155924</v>
       </c>
       <c r="P21" t="n">
         <v>2965</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11280</v>
+        <v>11460</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-20.95%</t>
+          <t>'-19.69%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.23</v>
       </c>
       <c r="E22" t="n">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="F22" t="n">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="G22" t="n">
-        <v>1659</v>
+        <v>1748</v>
       </c>
       <c r="H22" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>9.83</v>
       </c>
       <c r="O22" t="n">
-        <v>253676286805</v>
+        <v>258807708115</v>
       </c>
       <c r="P22" t="n">
         <v>40350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>단기 악재 및 과매도 상황 언급. 공매도 세력과 증권사 창구 매도세 지적. 원전 계약 관련 정부 실수 및 과도한 공사비 삭감 요구 비판.</t>
+          <t>원전 계약 관련 불확실성 및 공매도 관련 논란. 단기 악재로 인한 과매도 진단.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['공매도', '과매도', '원전계약']</t>
+          <t>['원전 계약', '공매도', '과매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
